--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.89502508587037</v>
+        <v>8.270441576453935</v>
       </c>
       <c r="D2" t="n">
-        <v>49.78813858202577</v>
+        <v>8.090572519579188</v>
       </c>
       <c r="E2" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F2" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.43664711140023</v>
+        <v>6.733455155602538</v>
       </c>
       <c r="D3" t="n">
-        <v>39.97614395215363</v>
+        <v>6.496123392224964</v>
       </c>
       <c r="E3" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F3" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.52270896406284</v>
+        <v>3.822440206660212</v>
       </c>
       <c r="D4" t="n">
-        <v>21.98502984285827</v>
+        <v>3.572567349464469</v>
       </c>
       <c r="E4" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F4" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.69884698219246</v>
+        <v>3.688562634606274</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6946668726349</v>
+        <v>2.550383366803171</v>
       </c>
       <c r="E5" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F5" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.85702679664947</v>
+        <v>6.801766854455539</v>
       </c>
       <c r="D6" t="n">
-        <v>32.5073314942953</v>
+        <v>5.282441367822987</v>
       </c>
       <c r="E6" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F6" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.13470594446655</v>
+        <v>9.284389715975815</v>
       </c>
       <c r="D7" t="n">
-        <v>48.70498745921865</v>
+        <v>7.914560462123031</v>
       </c>
       <c r="E7" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F7" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.6371382760355</v>
+        <v>9.203534969855768</v>
       </c>
       <c r="D8" t="n">
-        <v>38.54076456875776</v>
+        <v>6.262874242423136</v>
       </c>
       <c r="E8" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F8" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.98253154616643</v>
+        <v>8.284661376252046</v>
       </c>
       <c r="D9" t="n">
-        <v>9.23276455491694</v>
+        <v>1.500324240174003</v>
       </c>
       <c r="E9" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F9" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.23138056439366</v>
+        <v>3.77509934171397</v>
       </c>
       <c r="D10" t="n">
-        <v>23.57337156611982</v>
+        <v>3.830672879494472</v>
       </c>
       <c r="E10" t="n">
-        <v>13.57860919614101</v>
+        <v>2.206523994372915</v>
       </c>
       <c r="F10" t="n">
-        <v>13.54230206037762</v>
+        <v>2.200624084811363</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
